--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_coquimbo.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:47</t>
+    <t xml:space="preserve">2026-09-24 00:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -555,13 +555,13 @@
         <v>10</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.07</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>10</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="4">
@@ -601,13 +601,13 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="F4" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <v>-0.04</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>-0.07</v>
       </c>
     </row>
     <row r="5">
@@ -624,13 +624,13 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.53</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>-0.05</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="6">
@@ -670,13 +670,13 @@
         <v>16</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="8">
@@ -696,10 +696,10 @@
         <v>0.43</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -719,10 +719,10 @@
         <v>0.48</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="10">
@@ -739,13 +739,13 @@
         <v>16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="11">
@@ -762,13 +762,13 @@
         <v>16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="12">
@@ -785,13 +785,13 @@
         <v>16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="13">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="14">
@@ -834,10 +834,10 @@
         <v>-0.51</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="15">
@@ -854,13 +854,13 @@
         <v>16</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="16">
@@ -877,13 +877,13 @@
         <v>16</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.59</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>-0.38</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="17">
@@ -900,13 +900,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.45</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="18">
@@ -946,13 +946,13 @@
         <v>10</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>-0.36</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="20">
@@ -969,13 +969,13 @@
         <v>10</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>-0.51</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="21">
@@ -992,13 +992,13 @@
         <v>10</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.4</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>-0.26</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="22">
@@ -1015,13 +1015,13 @@
         <v>10</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>0.26</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="23">
@@ -1067,7 +1067,7 @@
         <v>0.09</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="25">
@@ -1090,7 +1090,7 @@
         <v>-0.06</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="26">
@@ -1130,13 +1130,13 @@
         <v>16</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.69</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="28">
@@ -1153,13 +1153,13 @@
         <v>16</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.69</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.78</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="29">
@@ -1176,13 +1176,13 @@
         <v>16</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="30">
@@ -1199,13 +1199,13 @@
         <v>16</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="31">
@@ -1245,13 +1245,13 @@
         <v>16</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="33">
@@ -1268,7 +1268,7 @@
         <v>16</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>-0.04</v>
@@ -1291,13 +1291,13 @@
         <v>16</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.26</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>-0.21</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="35">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_coquimbo.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:37</t>
+    <t xml:space="preserve">2026-10-01 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2018_coquimbo.xlsx
@@ -120,7 +120,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:10</t>
+    <t xml:space="preserve">2026-10-05 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
